--- a/attendance_template.xlsx
+++ b/attendance_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yussif03\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yussif\Full Stack Dev\Iken\EMS_IKEN_Intern\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD35DDB-CCD4-4DC7-BBBF-B5149C722A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E8784-BE42-4463-886C-CBD5767982CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,10 +108,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1032,10 +1037,10 @@
       <c r="B47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1046,10 +1051,10 @@
       <c r="B48" t="s">
         <v>7</v>
       </c>
-      <c r="C48" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1060,10 +1065,10 @@
       <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="C49" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1074,10 +1079,10 @@
       <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1088,6 +1093,8 @@
       <c r="B51" t="s">
         <v>14</v>
       </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
@@ -1096,11 +1103,11 @@
       <c r="B52" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="2">
-        <v>0.38611111111111113</v>
-      </c>
-      <c r="D52" s="2">
-        <v>0.70833333333333337</v>
+      <c r="C52" s="3">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>

--- a/attendance_template.xlsx
+++ b/attendance_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yussif\Full Stack Dev\Iken\EMS_IKEN_Intern\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A5E8784-BE42-4463-886C-CBD5767982CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B8A9A8-2BC8-4907-B829-45CB913D23F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1104,7 +1104,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="3">
-        <v>0.42708333333333331</v>
+        <v>0.4375</v>
       </c>
       <c r="D52" s="3">
         <v>0.75</v>
